--- a/downloads/invoice-template.xlsx
+++ b/downloads/invoice-template.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="חשבונית" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'חשבונית'!$A$1:$D$1,'חשבונית'!$A$4:$D$21</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -109,7 +111,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -131,11 +133,55 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -178,6 +224,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,9 +589,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -715,65 +763,47 @@
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr"/>
-      <c r="B18" s="7" t="inlineStr"/>
-      <c r="C18" s="8" t="inlineStr"/>
-      <c r="D18" s="9">
-        <f>IF(OR(B18="",C18=""),"",B18*C18)</f>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>סכום ביניים:</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="12">
+        <f>SUM(D15:D17)</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr"/>
-      <c r="B19" s="7" t="inlineStr"/>
-      <c r="C19" s="8" t="inlineStr"/>
-      <c r="D19" s="9">
-        <f>IF(OR(B19="",C19=""),"",B19*C19)</f>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>מע"מ (17%):</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="12">
+        <f>D19*0.17</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>סכום ביניים:</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="12">
-        <f>SUM(D15:D19)</f>
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>סה"כ לתשלום:</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="14">
+        <f>D19+D20</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>מע"מ (17%):</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="12">
-        <f>D21*0.17</f>
-        <v/>
-      </c>
-    </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>סה"כ לתשלום:</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="14">
-        <f>D21+D22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>שיעור מע"מ בישראל נכון למועד יצירת התבנית: 17%. יש לעדכן בהתאם לשיעור העדכני.</t>
         </is>
@@ -783,18 +813,19 @@
   <mergeCells count="13">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A23:D23"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
     <mergeCell ref="B4:D4"/>
-    <mergeCell ref="A22:C22"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A25:D25"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/downloads/invoice-template.xlsx
+++ b/downloads/invoice-template.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="חשבונית" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'חשבונית'!$A$1:$D$1,'חשבונית'!$A$4:$D$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'חשבונית'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -607,7 +607,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>התאים הצהובים הם שדות למילוי — שאר התאים מתעדכנים אוטומטית</t>
@@ -802,7 +802,7 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
           <t>שיעור מע"מ בישראל נכון למועד יצירת התבנית: 17%. יש לעדכן בהתאם לשיעור העדכני.</t>
